--- a/Fujiya Instruments/Junk Guitar/Junk Guitar Free/xlsx/Junk Guitar Free.xlsx
+++ b/Fujiya Instruments/Junk Guitar/Junk Guitar Free/xlsx/Junk Guitar Free.xlsx
@@ -35,6 +35,21 @@
       <text>
         <r>
           <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
+      <text>
+        <r>
+          <rPr>
             <b/>
             <sz val="9"/>
             <color rgb="FF000000"/>
@@ -57,6 +72,21 @@
   </authors>
   <commentList>
     <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -85,6 +115,21 @@
       <text>
         <r>
           <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
+      <text>
+        <r>
+          <rPr>
             <b/>
             <sz val="9"/>
             <color rgb="FF000000"/>
@@ -110,6 +155,21 @@
       <text>
         <r>
           <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
+      <text>
+        <r>
+          <rPr>
             <b/>
             <sz val="9"/>
             <color rgb="FF000000"/>
@@ -126,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="198">
   <si>
     <t>Name</t>
   </si>
@@ -713,13 +773,28 @@
   <si>
     <t>Brush</t>
     <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>Expression Map Name</t>
+  </si>
+  <si>
+    <t>Junk Guitar Free (Mono)</t>
+  </si>
+  <si>
+    <t>Junk Guitar Free (Poly)</t>
+  </si>
+  <si>
+    <t>Junk Guitar Free (Chord)</t>
+  </si>
+  <si>
+    <t>Junk Guitar Free (Stop)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -764,8 +839,15 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -818,6 +900,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDBEEF4"/>
         <bgColor rgb="FFEBF1DE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39994506668294322"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -877,7 +965,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -937,6 +1025,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1027,13 +1121,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>55</xdr:row>
+      <xdr:row>57</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1332,7 +1426,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1340,7 +1434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M129"/>
+  <dimension ref="A1:M131"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="39.5" style="14" customWidth="1"/>
@@ -1355,118 +1449,65 @@
     <col min="1028" max="16384" width="8.875" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:13" ht="30" customHeight="1">
+      <c r="A1" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="C1" s="20"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H3" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I3" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M3" s="10" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="12">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="12">
-        <v>1</v>
-      </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B3" s="12">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="12">
-        <v>1</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="12">
-        <v>120</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="I3" s="12">
-        <v>120</v>
-      </c>
-      <c r="J3" s="12">
-        <v>2</v>
-      </c>
-      <c r="K3" s="12">
-        <v>0</v>
-      </c>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>146</v>
+        <v>11</v>
       </c>
       <c r="B4" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>146</v>
+        <v>11</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>12</v>
@@ -1474,36 +1515,24 @@
       <c r="E4" s="12">
         <v>1</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" s="12">
-        <v>120</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" s="12">
-        <v>120</v>
-      </c>
-      <c r="J4" s="12">
-        <v>2</v>
-      </c>
-      <c r="K4" s="12">
-        <v>127</v>
-      </c>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
       <c r="L4" s="12"/>
       <c r="M4" s="12"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B5" s="12">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>12</v>
@@ -1518,25 +1547,29 @@
         <v>120</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I5" s="12">
         <v>120</v>
       </c>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
+      <c r="J5" s="12">
+        <v>2</v>
+      </c>
+      <c r="K5" s="12">
+        <v>0</v>
+      </c>
       <c r="L5" s="12"/>
       <c r="M5" s="12"/>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B6" s="12">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>12</v>
@@ -1551,25 +1584,29 @@
         <v>120</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I6" s="12">
         <v>120</v>
       </c>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
+      <c r="J6" s="12">
+        <v>2</v>
+      </c>
+      <c r="K6" s="12">
+        <v>127</v>
+      </c>
       <c r="L6" s="12"/>
       <c r="M6" s="12"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B7" s="12">
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>12</v>
@@ -1584,7 +1621,7 @@
         <v>120</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I7" s="12">
         <v>120</v>
@@ -1596,13 +1633,13 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B8" s="12">
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>12</v>
@@ -1617,7 +1654,7 @@
         <v>120</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I8" s="12">
         <v>120</v>
@@ -1629,13 +1666,13 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B9" s="12">
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D9" s="13" t="s">
         <v>12</v>
@@ -1650,7 +1687,7 @@
         <v>120</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I9" s="12">
         <v>120</v>
@@ -1662,13 +1699,13 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B10" s="12">
         <v>1</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D10" s="13" t="s">
         <v>12</v>
@@ -1683,7 +1720,7 @@
         <v>120</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I10" s="12">
         <v>120</v>
@@ -1695,13 +1732,13 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B11" s="12">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D11" s="13" t="s">
         <v>12</v>
@@ -1716,7 +1753,7 @@
         <v>120</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I11" s="12">
         <v>120</v>
@@ -1728,13 +1765,13 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B12" s="12">
         <v>1</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D12" s="13" t="s">
         <v>12</v>
@@ -1749,7 +1786,7 @@
         <v>120</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I12" s="12">
         <v>120</v>
@@ -1761,13 +1798,13 @@
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B13" s="12">
         <v>1</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>12</v>
@@ -1782,7 +1819,7 @@
         <v>120</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I13" s="12">
         <v>120</v>
@@ -1794,13 +1831,13 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B14" s="12">
         <v>1</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>12</v>
@@ -1815,7 +1852,7 @@
         <v>120</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I14" s="12">
         <v>120</v>
@@ -1827,13 +1864,13 @@
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B15" s="12">
         <v>1</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>12</v>
@@ -1848,7 +1885,7 @@
         <v>120</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I15" s="12">
         <v>120</v>
@@ -1860,13 +1897,13 @@
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B16" s="12">
         <v>1</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>12</v>
@@ -1881,7 +1918,7 @@
         <v>120</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I16" s="12">
         <v>120</v>
@@ -1893,13 +1930,13 @@
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B17" s="12">
         <v>1</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>12</v>
@@ -1914,7 +1951,7 @@
         <v>120</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I17" s="12">
         <v>120</v>
@@ -1926,13 +1963,13 @@
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B18" s="12">
         <v>1</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>12</v>
@@ -1947,7 +1984,7 @@
         <v>120</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I18" s="12">
         <v>120</v>
@@ -1959,13 +1996,13 @@
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B19" s="12">
         <v>1</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>12</v>
@@ -1980,7 +2017,7 @@
         <v>120</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I19" s="12">
         <v>120</v>
@@ -1992,13 +2029,13 @@
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B20" s="12">
         <v>1</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>12</v>
@@ -2013,7 +2050,7 @@
         <v>120</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I20" s="12">
         <v>120</v>
@@ -2024,30 +2061,66 @@
       <c r="M20" s="12"/>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="1"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
+      <c r="A21" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B21" s="12">
+        <v>1</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="12">
+        <v>1</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="12">
+        <v>120</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I21" s="12">
+        <v>120</v>
+      </c>
       <c r="J21" s="12"/>
       <c r="K21" s="12"/>
       <c r="L21" s="12"/>
       <c r="M21" s="12"/>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="1"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
+      <c r="A22" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B22" s="12">
+        <v>1</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="12">
+        <v>1</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G22" s="12">
+        <v>120</v>
+      </c>
+      <c r="H22" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="I22" s="12">
+        <v>120</v>
+      </c>
       <c r="J22" s="12"/>
       <c r="K22" s="12"/>
       <c r="L22" s="12"/>
@@ -3658,26 +3731,59 @@
       <c r="L129" s="12"/>
       <c r="M129" s="12"/>
     </row>
+    <row r="130" spans="1:13">
+      <c r="A130" s="1"/>
+      <c r="B130" s="12"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="13"/>
+      <c r="E130" s="12"/>
+      <c r="F130" s="12"/>
+      <c r="G130" s="12"/>
+      <c r="H130" s="12"/>
+      <c r="I130" s="12"/>
+      <c r="J130" s="12"/>
+      <c r="K130" s="12"/>
+      <c r="L130" s="12"/>
+      <c r="M130" s="12"/>
+    </row>
+    <row r="131" spans="1:13">
+      <c r="A131" s="1"/>
+      <c r="B131" s="12"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="13"/>
+      <c r="E131" s="12"/>
+      <c r="F131" s="12"/>
+      <c r="G131" s="12"/>
+      <c r="H131" s="12"/>
+      <c r="I131" s="12"/>
+      <c r="J131" s="12"/>
+      <c r="K131" s="12"/>
+      <c r="L131" s="12"/>
+      <c r="M131" s="12"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="5"/>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B129">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B131">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="J2:K129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="J4:K131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="I2:I129 G2:G129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="I4:I131 G4:G131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="L2:L129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="L4:L131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="M2:M129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="M4:M131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
@@ -3696,7 +3802,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D129</xm:sqref>
+          <xm:sqref>D4:D131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -3705,7 +3811,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E2:E129</xm:sqref>
+          <xm:sqref>E4:E131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" promptTitle="MIDI Note" prompt="Choose from Drop-down list or imput number directly(0-127)_x000a__x000a_If don’t use MIDI Note, set Cell value empty.">
           <x14:formula1>
@@ -3714,7 +3820,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>H2:H129 F2:F129</xm:sqref>
+          <xm:sqref>H4:H131 F4:F131</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3724,7 +3830,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O131"/>
+  <dimension ref="A1:O133"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="39.5" style="14" customWidth="1"/>
@@ -3741,126 +3847,71 @@
     <col min="1030" max="16384" width="8.875" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:15" ht="30" customHeight="1">
+      <c r="A1" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="C1" s="20"/>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H3" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I3" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J3" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K3" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="N3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="O3" s="10" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="12">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="12">
-        <v>1</v>
-      </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
-    </row>
-    <row r="3" spans="1:15">
-      <c r="A3" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B3" s="12">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="12">
-        <v>1</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" s="12">
-        <v>120</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="I3" s="12">
-        <v>120</v>
-      </c>
-      <c r="J3" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="12"/>
-      <c r="O3" s="12"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="1" t="s">
-        <v>163</v>
+        <v>11</v>
       </c>
       <c r="B4" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>163</v>
+        <v>11</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>12</v>
@@ -3868,42 +3919,26 @@
       <c r="E4" s="12">
         <v>1</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="12">
-        <v>120</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="I4" s="12">
-        <v>120</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="K4" s="12">
-        <v>120</v>
-      </c>
-      <c r="L4" s="12">
-        <v>2</v>
-      </c>
-      <c r="M4" s="12">
-        <v>0</v>
-      </c>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="12"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B5" s="12">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>12</v>
@@ -3926,27 +3961,21 @@
       <c r="J5" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="K5" s="12">
-        <v>120</v>
-      </c>
-      <c r="L5" s="12">
-        <v>2</v>
-      </c>
-      <c r="M5" s="12">
-        <v>127</v>
-      </c>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="12"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B6" s="12">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>12</v>
@@ -3961,7 +3990,7 @@
         <v>120</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I6" s="12">
         <v>120</v>
@@ -3983,13 +4012,13 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B7" s="12">
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>12</v>
@@ -4004,7 +4033,7 @@
         <v>120</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I7" s="12">
         <v>120</v>
@@ -4026,13 +4055,13 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="1" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="B8" s="12">
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>12</v>
@@ -4047,27 +4076,35 @@
         <v>120</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I8" s="12">
         <v>120</v>
       </c>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="12"/>
+      <c r="J8" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" s="12">
+        <v>120</v>
+      </c>
+      <c r="L8" s="12">
+        <v>2</v>
+      </c>
+      <c r="M8" s="12">
+        <v>0</v>
+      </c>
       <c r="N8" s="12"/>
       <c r="O8" s="12"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="1" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="B9" s="12">
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="D9" s="13" t="s">
         <v>12</v>
@@ -4082,27 +4119,35 @@
         <v>120</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I9" s="12">
         <v>120</v>
       </c>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
-      <c r="M9" s="12"/>
+      <c r="J9" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="K9" s="12">
+        <v>120</v>
+      </c>
+      <c r="L9" s="12">
+        <v>2</v>
+      </c>
+      <c r="M9" s="12">
+        <v>127</v>
+      </c>
       <c r="N9" s="12"/>
       <c r="O9" s="12"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B10" s="12">
         <v>1</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D10" s="13" t="s">
         <v>12</v>
@@ -4117,7 +4162,7 @@
         <v>120</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I10" s="12">
         <v>120</v>
@@ -4131,13 +4176,13 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B11" s="12">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D11" s="13" t="s">
         <v>12</v>
@@ -4152,7 +4197,7 @@
         <v>120</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I11" s="12">
         <v>120</v>
@@ -4166,13 +4211,13 @@
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B12" s="12">
         <v>1</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D12" s="13" t="s">
         <v>12</v>
@@ -4187,7 +4232,7 @@
         <v>120</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I12" s="12">
         <v>120</v>
@@ -4201,13 +4246,13 @@
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B13" s="12">
         <v>1</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>12</v>
@@ -4222,7 +4267,7 @@
         <v>120</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I13" s="12">
         <v>120</v>
@@ -4236,13 +4281,13 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B14" s="12">
         <v>1</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>12</v>
@@ -4257,7 +4302,7 @@
         <v>120</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I14" s="12">
         <v>120</v>
@@ -4271,13 +4316,13 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B15" s="12">
         <v>1</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>12</v>
@@ -4292,7 +4337,7 @@
         <v>120</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I15" s="12">
         <v>120</v>
@@ -4306,13 +4351,13 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B16" s="12">
         <v>1</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>12</v>
@@ -4327,7 +4372,7 @@
         <v>120</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I16" s="12">
         <v>120</v>
@@ -4340,15 +4385,33 @@
       <c r="O16" s="12"/>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17" s="1"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
+      <c r="A17" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B17" s="12">
+        <v>1</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="12">
+        <v>1</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G17" s="12">
+        <v>120</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I17" s="12">
+        <v>120</v>
+      </c>
       <c r="J17" s="12"/>
       <c r="K17" s="12"/>
       <c r="L17" s="12"/>
@@ -4357,15 +4420,33 @@
       <c r="O17" s="12"/>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18" s="1"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
+      <c r="A18" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B18" s="12">
+        <v>1</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="12">
+        <v>1</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18" s="12">
+        <v>120</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="I18" s="12">
+        <v>120</v>
+      </c>
       <c r="J18" s="12"/>
       <c r="K18" s="12"/>
       <c r="L18" s="12"/>
@@ -6294,26 +6375,63 @@
       <c r="N131" s="12"/>
       <c r="O131" s="12"/>
     </row>
+    <row r="132" spans="1:15">
+      <c r="A132" s="1"/>
+      <c r="B132" s="12"/>
+      <c r="C132" s="2"/>
+      <c r="D132" s="13"/>
+      <c r="E132" s="12"/>
+      <c r="F132" s="12"/>
+      <c r="G132" s="12"/>
+      <c r="H132" s="12"/>
+      <c r="I132" s="12"/>
+      <c r="J132" s="12"/>
+      <c r="K132" s="12"/>
+      <c r="L132" s="12"/>
+      <c r="M132" s="12"/>
+      <c r="N132" s="12"/>
+      <c r="O132" s="12"/>
+    </row>
+    <row r="133" spans="1:15">
+      <c r="A133" s="1"/>
+      <c r="B133" s="12"/>
+      <c r="C133" s="2"/>
+      <c r="D133" s="13"/>
+      <c r="E133" s="12"/>
+      <c r="F133" s="12"/>
+      <c r="G133" s="12"/>
+      <c r="H133" s="12"/>
+      <c r="I133" s="12"/>
+      <c r="J133" s="12"/>
+      <c r="K133" s="12"/>
+      <c r="L133" s="12"/>
+      <c r="M133" s="12"/>
+      <c r="N133" s="12"/>
+      <c r="O133" s="12"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="6"/>
   <dataValidations count="5">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="O2:O131">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="O4:O133">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="N2:N131">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="N4:N133">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="K2:K131 I2:I131 G2:G131">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="K4:K133 I4:I133 G4:G133">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="L2:M131">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="L4:M133">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B131">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B133">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6331,7 +6449,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>J2:J131 H2:H131 F2:F131</xm:sqref>
+          <xm:sqref>J4:J133 H4:H133 F4:F133</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -6340,7 +6458,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E2:E131</xm:sqref>
+          <xm:sqref>E4:E133</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -6349,7 +6467,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D131</xm:sqref>
+          <xm:sqref>D4:D133</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6359,7 +6477,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M128"/>
+  <dimension ref="A1:M130"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="39.5" style="14" customWidth="1"/>
@@ -6374,114 +6492,65 @@
     <col min="1028" max="16384" width="8.875" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:13" ht="30" customHeight="1">
+      <c r="A1" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1" s="20"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H3" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I3" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M3" s="10" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="12">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="12">
-        <v>1</v>
-      </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="B3" s="12">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="12">
-        <v>1</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" s="12">
-        <v>120</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="I3" s="12">
-        <v>120</v>
-      </c>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>187</v>
+        <v>11</v>
       </c>
       <c r="B4" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>187</v>
+        <v>11</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>12</v>
@@ -6489,18 +6558,10 @@
       <c r="E4" s="12">
         <v>1</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="12">
-        <v>120</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="I4" s="12">
-        <v>120</v>
-      </c>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
       <c r="J4" s="12"/>
       <c r="K4" s="12"/>
       <c r="L4" s="12"/>
@@ -6508,13 +6569,13 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B5" s="12">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>192</v>
+      <c r="C5" s="2" t="s">
+        <v>186</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>12</v>
@@ -6529,7 +6590,7 @@
         <v>120</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I5" s="12">
         <v>120</v>
@@ -6541,13 +6602,13 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B6" s="12">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>12</v>
@@ -6562,7 +6623,7 @@
         <v>120</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I6" s="12">
         <v>120</v>
@@ -6574,13 +6635,13 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B7" s="12">
         <v>1</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>189</v>
+      <c r="C7" s="1" t="s">
+        <v>192</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>12</v>
@@ -6595,7 +6656,7 @@
         <v>120</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="I7" s="12">
         <v>120</v>
@@ -6606,30 +6667,66 @@
       <c r="M7" s="12"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="1"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
+      <c r="A8" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B8" s="12">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="12">
+        <v>1</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="12">
+        <v>120</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="I8" s="12">
+        <v>120</v>
+      </c>
       <c r="J8" s="12"/>
       <c r="K8" s="12"/>
       <c r="L8" s="12"/>
       <c r="M8" s="12"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="1"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
+      <c r="A9" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B9" s="12">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="12">
+        <v>1</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="12">
+        <v>120</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" s="12">
+        <v>120</v>
+      </c>
       <c r="J9" s="12"/>
       <c r="K9" s="12"/>
       <c r="L9" s="12"/>
@@ -8420,26 +8517,59 @@
       <c r="L128" s="12"/>
       <c r="M128" s="12"/>
     </row>
+    <row r="129" spans="1:13">
+      <c r="A129" s="1"/>
+      <c r="B129" s="12"/>
+      <c r="C129" s="2"/>
+      <c r="D129" s="13"/>
+      <c r="E129" s="12"/>
+      <c r="F129" s="12"/>
+      <c r="G129" s="12"/>
+      <c r="H129" s="12"/>
+      <c r="I129" s="12"/>
+      <c r="J129" s="12"/>
+      <c r="K129" s="12"/>
+      <c r="L129" s="12"/>
+      <c r="M129" s="12"/>
+    </row>
+    <row r="130" spans="1:13">
+      <c r="A130" s="1"/>
+      <c r="B130" s="12"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="13"/>
+      <c r="E130" s="12"/>
+      <c r="F130" s="12"/>
+      <c r="G130" s="12"/>
+      <c r="H130" s="12"/>
+      <c r="I130" s="12"/>
+      <c r="J130" s="12"/>
+      <c r="K130" s="12"/>
+      <c r="L130" s="12"/>
+      <c r="M130" s="12"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="6"/>
   <dataValidations count="5">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="M2:M128">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="M4:M130">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="L2:L128">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="L4:L130">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G2:G128 I2:I128">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G4:G130 I4:I130">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="J2:K128">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="J4:K130">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B128">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B130">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -8457,7 +8587,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>F2:F128 H2:H128</xm:sqref>
+          <xm:sqref>F4:F130 H4:H130</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -8466,7 +8596,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E2:E128</xm:sqref>
+          <xm:sqref>E4:E130</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -8475,7 +8605,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D128</xm:sqref>
+          <xm:sqref>D4:D130</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -8485,7 +8615,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K131"/>
+  <dimension ref="A1:K133"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="39.5" style="14" customWidth="1"/>
@@ -8498,100 +8628,59 @@
     <col min="1026" max="16384" width="8.875" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:11" ht="30" customHeight="1">
+      <c r="A1" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="C1" s="20"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K3" s="10" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="12">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="12">
-        <v>1</v>
-      </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="B3" s="12">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="12">
-        <v>1</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="G3" s="12">
-        <v>31</v>
-      </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>171</v>
+        <v>11</v>
       </c>
       <c r="B4" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>171</v>
+        <v>11</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>12</v>
@@ -8599,12 +8688,8 @@
       <c r="E4" s="12">
         <v>1</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="G4" s="12">
-        <v>64</v>
-      </c>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
@@ -8612,13 +8697,13 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B5" s="12">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>12</v>
@@ -8630,7 +8715,7 @@
         <v>51</v>
       </c>
       <c r="G5" s="12">
-        <v>96</v>
+        <v>31</v>
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
@@ -8639,13 +8724,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B6" s="12">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>12</v>
@@ -8657,7 +8742,7 @@
         <v>51</v>
       </c>
       <c r="G6" s="12">
-        <v>127</v>
+        <v>64</v>
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
@@ -8666,13 +8751,13 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B7" s="12">
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>12</v>
@@ -8681,10 +8766,10 @@
         <v>1</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G7" s="12">
-        <v>31</v>
+        <v>96</v>
       </c>
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
@@ -8693,13 +8778,13 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B8" s="12">
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>12</v>
@@ -8708,10 +8793,10 @@
         <v>1</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G8" s="12">
-        <v>64</v>
+        <v>127</v>
       </c>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
@@ -8720,13 +8805,13 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B9" s="12">
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D9" s="13" t="s">
         <v>12</v>
@@ -8738,7 +8823,7 @@
         <v>53</v>
       </c>
       <c r="G9" s="12">
-        <v>96</v>
+        <v>31</v>
       </c>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
@@ -8747,13 +8832,13 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B10" s="12">
         <v>1</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D10" s="13" t="s">
         <v>12</v>
@@ -8765,7 +8850,7 @@
         <v>53</v>
       </c>
       <c r="G10" s="12">
-        <v>127</v>
+        <v>64</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
@@ -8774,13 +8859,13 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B11" s="12">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D11" s="13" t="s">
         <v>12</v>
@@ -8789,10 +8874,10 @@
         <v>1</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G11" s="12">
-        <v>31</v>
+        <v>96</v>
       </c>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
@@ -8801,13 +8886,13 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B12" s="12">
         <v>1</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D12" s="13" t="s">
         <v>12</v>
@@ -8816,10 +8901,10 @@
         <v>1</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G12" s="12">
-        <v>64</v>
+        <v>127</v>
       </c>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
@@ -8828,13 +8913,13 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B13" s="12">
         <v>1</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>12</v>
@@ -8846,7 +8931,7 @@
         <v>52</v>
       </c>
       <c r="G13" s="12">
-        <v>96</v>
+        <v>31</v>
       </c>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
@@ -8855,13 +8940,13 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B14" s="12">
         <v>1</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>12</v>
@@ -8873,7 +8958,7 @@
         <v>52</v>
       </c>
       <c r="G14" s="12">
-        <v>127</v>
+        <v>64</v>
       </c>
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
@@ -8882,13 +8967,13 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B15" s="12">
         <v>1</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>12</v>
@@ -8897,10 +8982,10 @@
         <v>1</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G15" s="12">
-        <v>31</v>
+        <v>96</v>
       </c>
       <c r="H15" s="12"/>
       <c r="I15" s="12"/>
@@ -8909,13 +8994,13 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B16" s="12">
         <v>1</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>12</v>
@@ -8924,10 +9009,10 @@
         <v>1</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G16" s="12">
-        <v>64</v>
+        <v>127</v>
       </c>
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
@@ -8936,13 +9021,13 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B17" s="12">
         <v>1</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>12</v>
@@ -8954,7 +9039,7 @@
         <v>54</v>
       </c>
       <c r="G17" s="12">
-        <v>96</v>
+        <v>31</v>
       </c>
       <c r="H17" s="12"/>
       <c r="I17" s="12"/>
@@ -8963,13 +9048,13 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B18" s="12">
         <v>1</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>12</v>
@@ -8981,7 +9066,7 @@
         <v>54</v>
       </c>
       <c r="G18" s="12">
-        <v>127</v>
+        <v>64</v>
       </c>
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
@@ -8989,26 +9074,54 @@
       <c r="K18" s="12"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="1"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
+      <c r="A19" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B19" s="12">
+        <v>1</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="12">
+        <v>1</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="G19" s="12">
+        <v>96</v>
+      </c>
       <c r="H19" s="12"/>
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="1"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
+      <c r="A20" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B20" s="12">
+        <v>1</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="12">
+        <v>1</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="G20" s="12">
+        <v>127</v>
+      </c>
       <c r="H20" s="12"/>
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
@@ -10457,26 +10570,55 @@
       <c r="J131" s="12"/>
       <c r="K131" s="12"/>
     </row>
+    <row r="132" spans="1:11">
+      <c r="A132" s="1"/>
+      <c r="B132" s="12"/>
+      <c r="C132" s="2"/>
+      <c r="D132" s="13"/>
+      <c r="E132" s="12"/>
+      <c r="F132" s="12"/>
+      <c r="G132" s="12"/>
+      <c r="H132" s="12"/>
+      <c r="I132" s="12"/>
+      <c r="J132" s="12"/>
+      <c r="K132" s="12"/>
+    </row>
+    <row r="133" spans="1:11">
+      <c r="A133" s="1"/>
+      <c r="B133" s="12"/>
+      <c r="C133" s="2"/>
+      <c r="D133" s="13"/>
+      <c r="E133" s="12"/>
+      <c r="F133" s="12"/>
+      <c r="G133" s="12"/>
+      <c r="H133" s="12"/>
+      <c r="I133" s="12"/>
+      <c r="J133" s="12"/>
+      <c r="K133" s="12"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="6"/>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B131">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B133">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I131">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I133">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G2:G131">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G4:G133">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J2:J131">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J4:J133">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K2:K131">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K4:K133">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
@@ -10494,7 +10636,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D131</xm:sqref>
+          <xm:sqref>D4:D133</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -10503,7 +10645,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E2:E131</xm:sqref>
+          <xm:sqref>E4:E133</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" promptTitle="MIDI Note" prompt="Choose from Drop-down list or imput number directly(0-127)_x000a__x000a_If don’t use MIDI Note, set Cell value empty.">
           <x14:formula1>
@@ -10512,7 +10654,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>F2:F131</xm:sqref>
+          <xm:sqref>F4:F133</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
